--- a/data/availability/projects/horizon-egypt-developments/saada-north-coast.xlsx
+++ b/data/availability/projects/horizon-egypt-developments/saada-north-coast.xlsx
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1304,433 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SNC-2B-CH-149</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Chalets</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>149</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Roof 50 sqm, 100% North Facing</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>21500000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SNC-3B-CH-168</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chalets</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>168</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Garden 60 sqm, 100% North Facing</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SNC-TH-278</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Villas</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>278</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>100% North Facing</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SNC-LARGE-VILLA-394</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Villas</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>394</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>100% North Facing</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>78500000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SNC-ORIZO-3RD-ROW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Prime Beachfront Villas</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>450</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Orizo G+1 3rd Row</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>216000000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SNC-NISI-2ND-ROW</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Prime Beachfront Villas</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>520</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Nisi One Story 2nd Row</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>saada-north-coast</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SNC-MIRAKI-1ST-ROW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Prime Beachfront Villas</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fully Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>600</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Miraki One Story 1st Row Sea Front</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sea View &amp; Lagoons</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>320000000</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5%+5% over 9 yrs</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
